--- a/forms/trg/Formulir_TRG_thecore.xlsx
+++ b/forms/trg/Formulir_TRG_thecore.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Syarif Syakib, MD, Sp.U(K)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -945,7 +949,11 @@
           <t>Dr. Rini Rachmawarni, MD, Sp.PD-KGEH</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
@@ -974,7 +982,11 @@
           <t>Andi Yasmin Syauki, MD, Ph.D, Sp.GK, Subsp.PK</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -1003,7 +1015,11 @@
           <t>Aminuddin, MD, Ph.D, Sp.GK</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -1032,7 +1048,11 @@
           <t>Prof. Nasrum Massi, MD, Ph.D, Sp.MK(K)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1061,7 +1081,11 @@
           <t>Prof. Eric J Alm, Ph.D</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -1090,7 +1114,11 @@
           <t>Prof. Dr. Mathilde Poyet</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -1119,7 +1147,11 @@
           <t>Prof. Dr. Mathiue</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -1148,7 +1180,11 @@
           <t>Prof. Varocha Mahavichai</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
           <t>(Thammasat University, Thailand)</t>
@@ -1177,7 +1213,11 @@
           <t>Prof. Ratha Korn</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
           <t>(Thammasat University, Thailand)</t>
@@ -1206,7 +1246,11 @@
           <t>Nurul Fauzani Jamaluddin, Ph.D</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
@@ -1295,7 +1339,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>STUDENT</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1328,7 +1372,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>STUDENT</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1361,7 +1405,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>STUDENT</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
